--- a/jonathan-harris-site-url-inventory-remediated-release-ready.xlsx
+++ b/jonathan-harris-site-url-inventory-remediated-release-ready.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ebook Source of Truth" sheetId="1" r:id="R7df272b882e341e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pages" sheetId="2" r:id="Ra665c114a7f54be5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="Ra1fa0f9d1e094c42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuyNow Redirects" sheetId="4" r:id="R7b42253624a24529"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ebooks Master" sheetId="5" r:id="Ra0cf0ea37d054655"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ebook Source of Truth" sheetId="1" r:id="R7e98cda51a0c4e59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pages" sheetId="2" r:id="Rf6c6bb0b64c042c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R4532bef954de461c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuyNow Redirects" sheetId="4" r:id="Re280fb3155bb4bc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ebooks Master" sheetId="5" r:id="Rc61a192e3ecb4ad4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8305,10 +8305,8 @@
         <x:f>$B$1&amp;B81</x:f>
         <x:v>https://jonathan-harris.online/newsletter/</x:v>
       </x:c>
-      <x:c r="D81" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Get the AI Edge | Jonathan Harris</x:t>
-        </x:is>
+      <x:c r="D81" s="18" t="str">
+        <x:v>AI Edge | Jonathan Harris</x:v>
       </x:c>
       <x:c r="E81" s="18" t="inlineStr">
         <x:is>
